--- a/Daily_Report/Top 7 broker List with its Turnover 2024-09-09.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-09-09.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="268">
   <si>
     <t>Date: 2024-09-09</t>
   </si>
@@ -59,103 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Stock Broker Opal Securities Investment Pvt. Limited</t>
+    <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Agrawal Securities Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+    <t>Sumeru Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>58</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>58</t>
+    <t>45</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>1,887,420,410.6</t>
-  </si>
-  <si>
-    <t>945,333,189.46</t>
-  </si>
-  <si>
-    <t>869,601,917.18</t>
-  </si>
-  <si>
-    <t>716,850,929.5</t>
-  </si>
-  <si>
-    <t>679,632,857.7</t>
-  </si>
-  <si>
-    <t>654,682,284.1</t>
-  </si>
-  <si>
-    <t>553,915,080.5</t>
-  </si>
-  <si>
-    <t>157,480,659.9</t>
-  </si>
-  <si>
-    <t>630,340,611.48</t>
-  </si>
-  <si>
-    <t>403,001,259.28</t>
-  </si>
-  <si>
-    <t>404,047,362.4</t>
-  </si>
-  <si>
-    <t>374,985,827.8</t>
-  </si>
-  <si>
-    <t>261,931,406.0</t>
-  </si>
-  <si>
-    <t>184,284,948.5</t>
-  </si>
-  <si>
-    <t>1,729,939,750.7</t>
-  </si>
-  <si>
-    <t>314,992,577.98</t>
-  </si>
-  <si>
-    <t>466,600,657.9</t>
-  </si>
-  <si>
-    <t>312,803,567.1</t>
-  </si>
-  <si>
-    <t>304,647,029.89</t>
-  </si>
-  <si>
-    <t>392,750,878.1</t>
-  </si>
-  <si>
-    <t>369,630,132.0</t>
+    <t>39</t>
+  </si>
+  <si>
+    <t>1,153,078,442.72</t>
+  </si>
+  <si>
+    <t>973,658,135.66</t>
+  </si>
+  <si>
+    <t>804,457,740.49</t>
+  </si>
+  <si>
+    <t>688,700,850.25</t>
+  </si>
+  <si>
+    <t>638,215,430.79</t>
+  </si>
+  <si>
+    <t>594,594,446.79</t>
+  </si>
+  <si>
+    <t>573,283,084.5</t>
+  </si>
+  <si>
+    <t>553,635,956.82</t>
+  </si>
+  <si>
+    <t>531,819,005.98</t>
+  </si>
+  <si>
+    <t>412,525,075.59</t>
+  </si>
+  <si>
+    <t>300,030,786.56</t>
+  </si>
+  <si>
+    <t>284,832,765.7</t>
+  </si>
+  <si>
+    <t>304,559,996.39</t>
+  </si>
+  <si>
+    <t>354,562,308.9</t>
+  </si>
+  <si>
+    <t>599,442,485.9</t>
+  </si>
+  <si>
+    <t>441,839,129.68</t>
+  </si>
+  <si>
+    <t>391,932,664.9</t>
+  </si>
+  <si>
+    <t>388,670,063.69</t>
+  </si>
+  <si>
+    <t>353,382,665.1</t>
+  </si>
+  <si>
+    <t>290,034,450.39</t>
+  </si>
+  <si>
+    <t>218,720,775.6</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -173,367 +179,307 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>DDBL</t>
-  </si>
-  <si>
-    <t>87,961,130.0</t>
-  </si>
-  <si>
-    <t>DLBS</t>
-  </si>
-  <si>
-    <t>24,507,520.0</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>8,536,150.0</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>6,051,650.0</t>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>44,234,167.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>34,007,795.9</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>29,405,827.2</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>25,263,645.2</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>22,704,568.3</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>12,515,754.4</t>
+  </si>
+  <si>
+    <t>12,443,968.8</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>11,606,535.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>10,979,936.4</t>
+  </si>
+  <si>
+    <t>NICAD85/86</t>
+  </si>
+  <si>
+    <t>10,808,000.0</t>
+  </si>
+  <si>
+    <t>19,051,175.39</t>
+  </si>
+  <si>
+    <t>16,958,141.7</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>16,696,801.1</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>4,510,005.0</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>122,810,080.0</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>114,480,420.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>101,292,701.0</t>
+    <t>15,449,816.2</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>11,902,847.8</t>
+  </si>
+  <si>
+    <t>14,536,342.0</t>
+  </si>
+  <si>
+    <t>12,996,257.3</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>12,394,556.4</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>12,121,596.6</t>
   </si>
   <si>
     <t>HATHY</t>
   </si>
   <si>
-    <t>42,174,124.0</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>38,661,672.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>53,558,367.7</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>32,106,904.9</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>29,658,273.9</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>24,581,250.0</t>
+    <t>10,174,625.0</t>
+  </si>
+  <si>
+    <t>11,032,833.8</t>
+  </si>
+  <si>
+    <t>10,020,499.4</t>
+  </si>
+  <si>
+    <t>9,455,607.0</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>7,190,067.6</t>
+  </si>
+  <si>
+    <t>6,790,956.7</t>
+  </si>
+  <si>
+    <t>26,843,171.3</t>
+  </si>
+  <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>11,799,819.4</t>
+  </si>
+  <si>
+    <t>8,037,903.7</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>6,984,324.5</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>6,244,047.0</t>
+  </si>
+  <si>
+    <t>91,274,170.7</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>72,556,069.8</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>19,138,129.2</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>10,799,366.4</t>
+  </si>
+  <si>
+    <t>10,361,856.4</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>25,062,490.0</t>
+  </si>
+  <si>
+    <t>24,516,081.4</t>
+  </si>
+  <si>
+    <t>23,179,713.0</t>
+  </si>
+  <si>
+    <t>22,069,150.8</t>
+  </si>
+  <si>
+    <t>21,602,698.2</t>
+  </si>
+  <si>
+    <t>11,234,545.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>11,208,965.8</t>
+  </si>
+  <si>
+    <t>11,044,471.9</t>
+  </si>
+  <si>
+    <t>SAND2085</t>
+  </si>
+  <si>
+    <t>10,765,000.0</t>
+  </si>
+  <si>
+    <t>12,904,444.7</t>
+  </si>
+  <si>
+    <t>12,350,167.8</t>
+  </si>
+  <si>
+    <t>9,950,616.8</t>
+  </si>
+  <si>
+    <t>9,602,970.69</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>8,308,820.2</t>
+  </si>
+  <si>
+    <t>35,156,986.9</t>
+  </si>
+  <si>
+    <t>23,298,910.6</t>
+  </si>
+  <si>
+    <t>14,116,705.1</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>12,949,021.9</t>
+  </si>
+  <si>
+    <t>9,222,788.9</t>
+  </si>
+  <si>
+    <t>27,279,424.9</t>
   </si>
   <si>
     <t>SHIVM</t>
   </si>
   <si>
-    <t>21,701,707.0</t>
-  </si>
-  <si>
-    <t>GBBL</t>
-  </si>
-  <si>
-    <t>80,186,400.0</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>61,330,628.0</t>
-  </si>
-  <si>
-    <t>TSHL</t>
-  </si>
-  <si>
-    <t>48,143,620.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>31,919,600.0</t>
-  </si>
-  <si>
-    <t>HBL</t>
-  </si>
-  <si>
-    <t>21,100,735.0</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>90,179,250.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>55,739,432.0</t>
-  </si>
-  <si>
-    <t>CHCL</t>
-  </si>
-  <si>
-    <t>47,417,995.0</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>26,577,681.5</t>
-  </si>
-  <si>
-    <t>18,044,495.0</t>
-  </si>
-  <si>
-    <t>63,914,054.5</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>37,664,116.5</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>34,634,402.0</t>
+    <t>11,604,334.9</t>
+  </si>
+  <si>
+    <t>10,552,216.6</t>
+  </si>
+  <si>
+    <t>10,100,301.1</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>9,469,203.8</t>
+  </si>
+  <si>
+    <t>12,770,498.9</t>
+  </si>
+  <si>
+    <t>11,446,467.5</t>
+  </si>
+  <si>
+    <t>6,991,688.2</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>6,798,038.2</t>
+  </si>
+  <si>
+    <t>6,182,982.5</t>
+  </si>
+  <si>
+    <t>38,182,913.5</t>
+  </si>
+  <si>
+    <t>18,479,967.1</t>
   </si>
   <si>
     <t>AKPL</t>
   </si>
   <si>
-    <t>13,701,244.4</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>12,548,751.0</t>
-  </si>
-  <si>
-    <t>NESDO</t>
-  </si>
-  <si>
-    <t>42,963,235.0</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>29,675,086.3</t>
-  </si>
-  <si>
-    <t>25,648,451.8</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>8,992,320.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>6,452,090.4</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>711,939,684.6</t>
-  </si>
-  <si>
-    <t>434,506,193.7</t>
-  </si>
-  <si>
-    <t>347,104,011.5</t>
-  </si>
-  <si>
-    <t>UMRH</t>
-  </si>
-  <si>
-    <t>112,372,320.0</t>
-  </si>
-  <si>
-    <t>61,887,070.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>72,720,400.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>44,803,728.0</t>
-  </si>
-  <si>
-    <t>36,766,830.0</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>23,280,510.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>17,309,748.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>156,214,996.0</t>
-  </si>
-  <si>
-    <t>42,004,120.0</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>28,431,207.0</t>
-  </si>
-  <si>
-    <t>23,917,027.0</t>
-  </si>
-  <si>
-    <t>22,962,344.9</t>
-  </si>
-  <si>
-    <t>70,769,222.0</t>
+    <t>9,845,748.69</t>
+  </si>
+  <si>
+    <t>6,971,292.0</t>
   </si>
   <si>
     <t>ICFC</t>
   </si>
   <si>
-    <t>64,951,579.0</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>46,738,659.9</t>
-  </si>
-  <si>
-    <t>VLBS</t>
-  </si>
-  <si>
-    <t>31,956,408.7</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>20,083,390.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>39,803,489.2</t>
-  </si>
-  <si>
-    <t>39,018,499.2</t>
-  </si>
-  <si>
-    <t>38,682,603.29</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>34,194,618.0</t>
-  </si>
-  <si>
-    <t>BARUN</t>
-  </si>
-  <si>
-    <t>29,864,280.0</t>
-  </si>
-  <si>
-    <t>168,118,820.1</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>122,184,250.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>22,160,299.0</t>
-  </si>
-  <si>
-    <t>10,027,041.0</t>
-  </si>
-  <si>
-    <t>9,492,611.0</t>
-  </si>
-  <si>
-    <t>80,947,163.09</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>48,087,100.2</t>
-  </si>
-  <si>
-    <t>33,130,640.0</t>
-  </si>
-  <si>
-    <t>DOLTI</t>
-  </si>
-  <si>
-    <t>29,832,077.0</t>
-  </si>
-  <si>
-    <t>29,446,505.5</t>
+    <t>6,771,850.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -551,109 +497,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>726,439,708.3</t>
-  </si>
-  <si>
-    <t>579,595,334.5</t>
-  </si>
-  <si>
-    <t>399,138,868.1</t>
-  </si>
-  <si>
-    <t>373,862,491.4</t>
-  </si>
-  <si>
-    <t>244,348,561.4</t>
+    <t>370,057,802.2</t>
+  </si>
+  <si>
+    <t>279,412,096.8</t>
+  </si>
+  <si>
+    <t>239,272,872.4</t>
+  </si>
+  <si>
+    <t>231,503,744.2</t>
+  </si>
+  <si>
+    <t>214,518,704.8</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>2,350,291,851.94</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,479,108,853.19</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>2,404,532,474.3</t>
+    <t>2,036,566,927.8</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>942,767,068.9</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>833,624,739.8</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>1,444,361,525.5</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>747,194,826.5</t>
+    <t>808,426,963.3</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>667,285,818.0</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>689,671,550.8</t>
+    <t>657,107,952.5</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>542,689,907.4</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>389,396,326.3</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>388,482,753.3</t>
+    <t>361,680,822.9</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>228,693,176.3</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>267,589,150.9</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>138,230,573.6</t>
+    <t>186,905,388.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>94,827,274.4</t>
+    <t>172,139,104.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>40,900,601.29</t>
+    <t>143,416,317.9</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>33,499,547.4</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>13,724,833.11</t>
+    <t>15,323,766.79</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>8,491,387.0</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>7,925,413.9</t>
+    <t>1,376,979.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -665,214 +611,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>114,491,477.5</t>
-  </si>
-  <si>
-    <t>22,721,399.1</t>
-  </si>
-  <si>
-    <t>9,615,542.0</t>
-  </si>
-  <si>
-    <t>3,033,318.0</t>
-  </si>
-  <si>
-    <t>2,985,257.4</t>
-  </si>
-  <si>
-    <t>312,473,098.7</t>
-  </si>
-  <si>
-    <t>155,494,612.9</t>
-  </si>
-  <si>
-    <t>76,591,952.5</t>
-  </si>
-  <si>
-    <t>30,535,762.0</t>
-  </si>
-  <si>
-    <t>19,415,896.0</t>
-  </si>
-  <si>
-    <t>152,077,736.1</t>
-  </si>
-  <si>
-    <t>68,870,064.8</t>
-  </si>
-  <si>
-    <t>51,295,433.4</t>
-  </si>
-  <si>
-    <t>32,598,376.1</t>
-  </si>
-  <si>
-    <t>30,815,167.3</t>
-  </si>
-  <si>
-    <t>145,407,465.19</t>
-  </si>
-  <si>
-    <t>106,698,440.3</t>
-  </si>
-  <si>
-    <t>52,160,442.7</t>
-  </si>
-  <si>
-    <t>39,364,507.5</t>
-  </si>
-  <si>
-    <t>38,672,807.7</t>
-  </si>
-  <si>
-    <t>93,556,813.6</t>
-  </si>
-  <si>
-    <t>90,436,341.5</t>
-  </si>
-  <si>
-    <t>66,007,674.2</t>
-  </si>
-  <si>
-    <t>42,801,754.0</t>
-  </si>
-  <si>
-    <t>31,937,136.5</t>
-  </si>
-  <si>
-    <t>121,485,654.4</t>
-  </si>
-  <si>
-    <t>75,255,355.09</t>
-  </si>
-  <si>
-    <t>16,135,134.6</t>
-  </si>
-  <si>
-    <t>13,330,336.6</t>
-  </si>
-  <si>
-    <t>10,756,017.0</t>
-  </si>
-  <si>
-    <t>76,585,221.3</t>
-  </si>
-  <si>
-    <t>32,455,016.3</t>
-  </si>
-  <si>
-    <t>23,525,721.9</t>
-  </si>
-  <si>
-    <t>21,989,777.7</t>
-  </si>
-  <si>
-    <t>9,336,172.0</t>
-  </si>
-  <si>
-    <t>749,108,128.5</t>
-  </si>
-  <si>
-    <t>442,402,294.9</t>
-  </si>
-  <si>
-    <t>350,613,126.1</t>
-  </si>
-  <si>
-    <t>180,666,653.0</t>
-  </si>
-  <si>
-    <t>3,262,207.6</t>
-  </si>
-  <si>
-    <t>100,751,196.3</t>
-  </si>
-  <si>
-    <t>87,952,370.9</t>
-  </si>
-  <si>
-    <t>79,225,640.0</t>
-  </si>
-  <si>
-    <t>14,933,639.1</t>
-  </si>
-  <si>
-    <t>11,561,827.5</t>
-  </si>
-  <si>
-    <t>266,927,369.6</t>
-  </si>
-  <si>
-    <t>66,370,516.3</t>
-  </si>
-  <si>
-    <t>29,393,135.1</t>
-  </si>
-  <si>
-    <t>26,519,522.6</t>
-  </si>
-  <si>
-    <t>20,349,852.8</t>
-  </si>
-  <si>
-    <t>140,385,914.19</t>
-  </si>
-  <si>
-    <t>72,609,279.0</t>
-  </si>
-  <si>
-    <t>35,396,537.69</t>
-  </si>
-  <si>
-    <t>33,459,600.7</t>
-  </si>
-  <si>
-    <t>9,789,639.69</t>
-  </si>
-  <si>
-    <t>130,065,778.9</t>
-  </si>
-  <si>
-    <t>57,150,463.7</t>
-  </si>
-  <si>
-    <t>46,401,218.6</t>
-  </si>
-  <si>
-    <t>27,979,083.5</t>
-  </si>
-  <si>
-    <t>10,223,888.3</t>
-  </si>
-  <si>
-    <t>294,157,693.89</t>
-  </si>
-  <si>
-    <t>29,045,546.0</t>
-  </si>
-  <si>
-    <t>27,390,213.7</t>
-  </si>
-  <si>
-    <t>21,123,634.7</t>
-  </si>
-  <si>
-    <t>8,460,509.7</t>
-  </si>
-  <si>
-    <t>144,149,655.9</t>
-  </si>
-  <si>
-    <t>106,365,841.7</t>
-  </si>
-  <si>
-    <t>73,637,706.3</t>
-  </si>
-  <si>
-    <t>20,357,714.89</t>
-  </si>
-  <si>
-    <t>6,407,063.1</t>
+    <t>128,202,551.1</t>
+  </si>
+  <si>
+    <t>109,892,150.2</t>
+  </si>
+  <si>
+    <t>74,783,744.3</t>
+  </si>
+  <si>
+    <t>58,239,574.4</t>
+  </si>
+  <si>
+    <t>40,818,478.6</t>
+  </si>
+  <si>
+    <t>221,333,114.4</t>
+  </si>
+  <si>
+    <t>94,819,799.9</t>
+  </si>
+  <si>
+    <t>53,837,601.2</t>
+  </si>
+  <si>
+    <t>30,462,375.6</t>
+  </si>
+  <si>
+    <t>28,531,223.1</t>
+  </si>
+  <si>
+    <t>100,040,249.8</t>
+  </si>
+  <si>
+    <t>97,508,820.2</t>
+  </si>
+  <si>
+    <t>39,313,628.4</t>
+  </si>
+  <si>
+    <t>36,506,413.4</t>
+  </si>
+  <si>
+    <t>34,790,497.2</t>
+  </si>
+  <si>
+    <t>74,192,676.0</t>
+  </si>
+  <si>
+    <t>67,650,101.0</t>
+  </si>
+  <si>
+    <t>36,657,633.2</t>
+  </si>
+  <si>
+    <t>23,162,075.9</t>
+  </si>
+  <si>
+    <t>21,084,098.5</t>
+  </si>
+  <si>
+    <t>82,716,441.59</t>
+  </si>
+  <si>
+    <t>78,498,279.9</t>
+  </si>
+  <si>
+    <t>29,379,743.5</t>
+  </si>
+  <si>
+    <t>21,832,940.9</t>
+  </si>
+  <si>
+    <t>17,124,676.6</t>
+  </si>
+  <si>
+    <t>92,527,444.6</t>
+  </si>
+  <si>
+    <t>74,474,679.0</t>
+  </si>
+  <si>
+    <t>32,546,530.1</t>
+  </si>
+  <si>
+    <t>20,949,682.7</t>
+  </si>
+  <si>
+    <t>20,040,758.1</t>
+  </si>
+  <si>
+    <t>171,065,447.3</t>
+  </si>
+  <si>
+    <t>41,497,140.2</t>
+  </si>
+  <si>
+    <t>26,955,532.8</t>
+  </si>
+  <si>
+    <t>25,478,607.7</t>
+  </si>
+  <si>
+    <t>23,070,010.4</t>
+  </si>
+  <si>
+    <t>163,236,590.19</t>
+  </si>
+  <si>
+    <t>103,513,974.6</t>
+  </si>
+  <si>
+    <t>62,527,133.1</t>
+  </si>
+  <si>
+    <t>61,142,527.9</t>
+  </si>
+  <si>
+    <t>51,774,504.6</t>
+  </si>
+  <si>
+    <t>189,908,254.5</t>
+  </si>
+  <si>
+    <t>84,402,223.8</t>
+  </si>
+  <si>
+    <t>39,176,218.0</t>
+  </si>
+  <si>
+    <t>31,123,989.9</t>
+  </si>
+  <si>
+    <t>21,070,178.39</t>
+  </si>
+  <si>
+    <t>90,966,736.7</t>
+  </si>
+  <si>
+    <t>77,061,204.7</t>
+  </si>
+  <si>
+    <t>55,599,987.7</t>
+  </si>
+  <si>
+    <t>33,924,131.79</t>
+  </si>
+  <si>
+    <t>29,489,960.6</t>
+  </si>
+  <si>
+    <t>81,363,881.2</t>
+  </si>
+  <si>
+    <t>80,553,867.2</t>
+  </si>
+  <si>
+    <t>73,571,480.9</t>
+  </si>
+  <si>
+    <t>34,481,732.7</t>
+  </si>
+  <si>
+    <t>29,517,056.9</t>
+  </si>
+  <si>
+    <t>71,236,342.0</t>
+  </si>
+  <si>
+    <t>67,295,892.2</t>
+  </si>
+  <si>
+    <t>36,752,893.7</t>
+  </si>
+  <si>
+    <t>34,624,246.79</t>
+  </si>
+  <si>
+    <t>33,198,763.2</t>
+  </si>
+  <si>
+    <t>75,561,148.09</t>
+  </si>
+  <si>
+    <t>70,146,546.8</t>
+  </si>
+  <si>
+    <t>32,107,594.2</t>
+  </si>
+  <si>
+    <t>22,043,081.8</t>
+  </si>
+  <si>
+    <t>21,195,958.6</t>
+  </si>
+  <si>
+    <t>57,146,989.5</t>
+  </si>
+  <si>
+    <t>51,727,568.6</t>
+  </si>
+  <si>
+    <t>44,173,653.2</t>
+  </si>
+  <si>
+    <t>23,442,789.0</t>
+  </si>
+  <si>
+    <t>11,173,111.7</t>
   </si>
 </sst>
 </file>
@@ -1449,37 +1395,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1489,37 +1435,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1529,37 +1475,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1569,1070 +1515,1070 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="L8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="O8" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="R8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="U8" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04660388830490482</v>
+        <v>0.0383618020779713</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1299119520707323</v>
+        <v>0.01285436226701492</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06158952348412761</v>
+        <v>0.02368200893734432</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1118592397668084</v>
+        <v>0.02110690293866092</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1326881844782826</v>
+        <v>0.01728700571556284</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="S9" s="16">
-        <v>0.09762606389733526</v>
+        <v>0.04514534477149107</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.0775628548715781</v>
+        <v>0.1592130889045968</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.01298466407503202</v>
+        <v>0.02949304630115095</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1211006037621448</v>
+        <v>0.01278063454126512</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.03692138237702867</v>
+        <v>0.02108021446803494</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.08555562317925404</v>
+        <v>0.0188706857197611</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P10" s="18">
-        <v>0.082014033560167</v>
+        <v>0.0157008102850778</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S10" s="16">
-        <v>0.05753037376256077</v>
+        <v>0.01984515574187499</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="V10" s="18">
-        <v>0.0535733496788232</v>
+        <v>0.1265623768810154</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.004522654280975168</v>
+        <v>0.02550201799856262</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.1071502641918889</v>
+        <v>0.01192054436245473</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="J11" s="14">
+        <v>0.02075534892588625</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.01799701045163622</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.01481569787202958</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="14">
-        <v>0.03410557556747083</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.06715987664768733</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.06977001547640152</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>104</v>
-      </c>
       <c r="R11" s="15" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05290261068788863</v>
+        <v>0.01351829594652044</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04630394207149592</v>
+        <v>0.03338338373735847</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.003206307384413743</v>
+        <v>0.02190973680889005</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04461297293929879</v>
+        <v>0.01127699343112579</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.02826724448781533</v>
+        <v>0.01920525519536853</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04452752822998188</v>
+        <v>0.01760067029915795</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="O12" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.0112658943250358</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="P12" s="18">
-        <v>0.03910593962443731</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>106</v>
-      </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02092808180816329</v>
+        <v>0.01174636685153784</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01623411298331676</v>
+        <v>0.01883775518933875</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.002389507379845646</v>
+        <v>0.01969039352296114</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04089740255717098</v>
+        <v>0.01110040537243982</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.02495590979189152</v>
+        <v>0.01479611320881804</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.0294353179045435</v>
+        <v>0.01477364954073541</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02655035699872696</v>
+        <v>0.01064053981190578</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01916769600272738</v>
+        <v>0.01050135438298211</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01164815804288253</v>
+        <v>0.01807458946575634</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3772024932027086</v>
+        <v>0.02173528623159411</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.01153849034742014</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.01604117164953851</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.05104826992334616</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="12">
-        <v>0.07692568166525483</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="O16" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.1796396637516438</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" s="15" t="s">
+      <c r="P16" s="18">
+        <v>0.04274328633170992</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="M16" s="16">
-        <v>0.09872236902777148</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.05856616370006326</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="S16" s="16">
-        <v>0.2567945157262275</v>
+        <v>0.021477662579475</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1461364132331111</v>
+        <v>0.06660394233208881</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D17" s="10">
-        <v>0.2302116641632973</v>
+        <v>0.02126141682275227</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04739464190989962</v>
+        <v>0.01151221911415749</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I17" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.01535216479174834</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.03383023353542026</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="J17" s="14">
-        <v>0.04830269939630954</v>
-      </c>
-      <c r="K17" s="15" t="s">
+      <c r="P17" s="18">
+        <v>0.01818247309604223</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.09060681423026598</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.05741114302808376</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="S17" s="16">
-        <v>0.1866313675616994</v>
+        <v>0.01925088194416013</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="V17" s="18">
-        <v>0.08681312694464545</v>
+        <v>0.03223532596660804</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1839039196305277</v>
+        <v>0.02010245976442098</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03889298546790916</v>
+        <v>0.01134327490881945</v>
       </c>
       <c r="H18" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.01236934682726655</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.02049758628129413</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.03269450818622677</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.06519997111896052</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>154</v>
-      </c>
       <c r="P18" s="18">
-        <v>0.05691691162624022</v>
+        <v>0.01653394150431751</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03384893640502896</v>
+        <v>0.01175875125916161</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05981176748265116</v>
+        <v>0.01717432271455761</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0595375144662537</v>
+        <v>0.01913933170751247</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.01110040537243982</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.01193719721579256</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="12">
-        <v>0.02462677737285248</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.02750342027483063</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>147</v>
-      </c>
       <c r="L19" s="15" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04457887600465196</v>
+        <v>0.01880209948237972</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05031336789060015</v>
+        <v>0.01582584909822585</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01531588870437253</v>
+        <v>0.01143306708729928</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05385676983748414</v>
+        <v>0.01216029600119834</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03278923426515582</v>
+        <v>0.01873480363490391</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.01105624202760128</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.01032847318361192</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="12">
-        <v>0.01831073762457002</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="13" t="s">
+      <c r="M20" s="16">
+        <v>0.01339157472602525</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.02640558219382006</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.02801613163005601</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>158</v>
-      </c>
       <c r="P20" s="18">
-        <v>0.04394178365811521</v>
+        <v>0.01483700227700606</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01449956907425655</v>
+        <v>0.01039865497109113</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05316068570189433</v>
+        <v>0.01181240295255912</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2626423245416658</v>
+        <v>0.248995163948005</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2547415365287016</v>
+        <v>0.2157584453428271</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1530188833968327</v>
+        <v>0.09987884725497893</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07915948743604231</v>
+        <v>0.088316065336906</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07306534323354073</v>
+        <v>0.08564655666055283</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05749377991242993</v>
+        <v>0.07069374874241079</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04125351582501339</v>
+        <v>0.06961548295737195</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04115672986257016</v>
+        <v>0.03831727354205657</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02834899182574812</v>
+        <v>0.02422826547237672</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01464445545671363</v>
+        <v>0.01980117400671297</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01004621307621023</v>
+        <v>0.01823680086223332</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D42" s="22">
-        <v>0.004333100979700005</v>
+        <v>0.01519384478089464</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D43" s="22">
-        <v>0.00145403944941905</v>
+        <v>0.003549016812582821</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0008995964890303923</v>
+        <v>0.001623434051822691</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D45" s="22">
-        <v>0.000839636035732757</v>
+        <v>0.0001458802282676058</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2785,37 +2731,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2825,37 +2771,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2865,37 +2811,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2905,835 +2851,835 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="L8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="O8" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="R8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="U8" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D9" s="10">
-        <v>0.06066029426035709</v>
+        <v>0.1111828530915751</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="G9" s="12">
-        <v>0.330542820440371</v>
+        <v>0.2273211780333639</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1748820156620253</v>
+        <v>0.124357371139303</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2028419845970221</v>
+        <v>0.1077284512906698</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1376578729824998</v>
+        <v>0.1296058315235583</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1855642917953826</v>
+        <v>0.15561437732553</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1382616650026375</v>
+        <v>0.2983961186456392</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="D10" s="10">
-        <v>0.01203833495303624</v>
+        <v>0.09530327350563861</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="G10" s="12">
-        <v>0.164486569004123</v>
+        <v>0.09738510512801891</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="J10" s="14">
-        <v>0.07919723202006752</v>
+        <v>0.1212106183981856</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1488432753716615</v>
+        <v>0.09822857191978615</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1330664644526647</v>
+        <v>0.1229965245459559</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1149494295594916</v>
+        <v>0.1252529003605891</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="V10" s="18">
-        <v>0.05859204315344507</v>
+        <v>0.07238507697500361</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D11" s="10">
-        <v>0.005094541706764353</v>
+        <v>0.06485573013020034</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="G11" s="12">
-        <v>0.08102111864257236</v>
+        <v>0.05529415225756405</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05898725886707342</v>
+        <v>0.04886972481121735</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07276330482877612</v>
+        <v>0.05322722222092974</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="P11" s="18">
-        <v>0.09712254705192132</v>
+        <v>0.04603421052225678</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02464574800917543</v>
+        <v>0.0547373596829899</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0424717122320702</v>
+        <v>0.04701958513830875</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D12" s="10">
-        <v>0.001607123660931337</v>
+        <v>0.05050790322869839</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03230158672144248</v>
+        <v>0.03128652088892668</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03748655040424943</v>
+        <v>0.04538015058163742</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="M12" s="16">
-        <v>0.05491310100895949</v>
+        <v>0.03363154828630183</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06297775852811008</v>
+        <v>0.03420935916988486</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02036153554746847</v>
+        <v>0.03523356602596511</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03969882473708892</v>
+        <v>0.04444332719536224</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D13" s="10">
-        <v>0.00158166001768043</v>
+        <v>0.03539956787650386</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02053868013572113</v>
+        <v>0.02930312196350102</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="J13" s="14">
-        <v>0.035435946829475</v>
+        <v>0.04324714083652039</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="M13" s="16">
-        <v>0.05394818658737612</v>
+        <v>0.03061430589543548</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="P13" s="18">
-        <v>0.04699174876282618</v>
+        <v>0.02683212560143571</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01642936926999091</v>
+        <v>0.03370491972781742</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01685487961723765</v>
+        <v>0.04024191716753854</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3968952143851527</v>
+        <v>0.1415659023291952</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1065774453106336</v>
+        <v>0.1950461332829818</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3069535201412721</v>
+        <v>0.1130783285702387</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1958369703139235</v>
+        <v>0.118141107522177</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1913765313527748</v>
+        <v>0.1116180188728837</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="S16" s="16">
-        <v>0.4493136610598563</v>
+        <v>0.1270801443011391</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2602378252093824</v>
+        <v>0.09968371829746531</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D17" s="10">
-        <v>0.2343952054430538</v>
+        <v>0.08977184098231911</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0930384883135657</v>
+        <v>0.08668568639113505</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="J17" s="14">
-        <v>0.07632287255671021</v>
+        <v>0.0957927319501725</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="M17" s="16">
-        <v>0.101289230454991</v>
+        <v>0.1169649597074822</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08409020113213399</v>
+        <v>0.1054438500737046</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="S17" s="16">
-        <v>0.04436586525314226</v>
+        <v>0.1179737671239886</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1920255386511363</v>
+        <v>0.09023041146437315</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D18" s="10">
-        <v>0.185763131590032</v>
+        <v>0.0542262614436747</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="G18" s="12">
-        <v>0.08380710725416912</v>
+        <v>0.04023611220938873</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03380067881556416</v>
+        <v>0.06911486446277926</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="M18" s="16">
-        <v>0.04937782214314614</v>
+        <v>0.1068264702639664</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="P18" s="18">
-        <v>0.06827394831531554</v>
+        <v>0.05758697130517579</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04183741391086162</v>
+        <v>0.05399914912222487</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="V18" s="18">
-        <v>0.1329404251524074</v>
+        <v>0.07705382278726558</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D19" s="10">
-        <v>0.09572146829892927</v>
+        <v>0.05302547132506503</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01579722289083122</v>
+        <v>0.03196603485360127</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03049616390681288</v>
+        <v>0.04217018507316072</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="M19" s="16">
-        <v>0.0466758140682581</v>
+        <v>0.05006779458379216</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04116793822283145</v>
+        <v>0.05425166037837517</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0322654747394592</v>
+        <v>0.03707246496941216</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03675241136533743</v>
+        <v>0.0408921693903564</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D20" s="10">
-        <v>0.001728394787763773</v>
+        <v>0.04490111225899686</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01223042587408195</v>
+        <v>0.02164022219741167</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02340134307200217</v>
+        <v>0.0366581849060679</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01365645114923437</v>
+        <v>0.0428590394353154</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01504325193252057</v>
+        <v>0.05201811425710205</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01292307720168535</v>
+        <v>0.03564775741528167</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="V20" s="18">
-        <v>0.0115668688677271</v>
+        <v>0.01948969366459652</v>
       </c>
     </row>
   </sheetData>
